--- a/datasets/general_data_dataset_tripadvisor.xlsx
+++ b/datasets/general_data_dataset_tripadvisor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>facilities</t>
         </is>
       </c>
@@ -471,6 +476,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>191 €</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Piscina, Lezioni di yoga, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Teli da piscina/mare, Piscina all'aperto, Corsi di fitness, Ristorante, Colazione a buffet, Drink di benvenuto omaggio, Noleggio di biciclette, Canoismo, Campo da tennis, Noleggi di attrezzature per sport acquatici, Windsurf, Tour in bicicletta, Personale di intrattenimento, Intrattenimento serale, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Servizio taxi, Sicurezza 24 ore su 24, Minimarket, Zanzariera, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Lavanderia self-service, Lavatrice, Camere insonorizzate, Aria condizionata, Spiaggia privata, Servizio di pulizia, Angolo cottura, TV a schermo piatto, Divano letto, Bidet, Cassaforte, Zona soggiorno, Divano, Armadio/cabina, Forno, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Asciugacapelli, Camere non fumatori, Camere per famiglie, </t>
         </is>
       </c>
@@ -496,6 +506,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>275 €</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Wi-Fi, Giochi da piscina, Piscina all'aperto, Piscina con estremità bassa, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Bar in piscina, Noleggio di biciclette, Canoismo, Escursioni, Campo da tennis, Parco acquatico, Windsurf, Aerobica, Personale di intrattenimento, Intrattenimento serale, Ping pong, Scivolo acquatico, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Passeggini, Animali domestici ammessi, Area barbecue, Minimarket, Negozio di articoli da regalo, Quotidiano, Negozi, Lettini/sedie sdraio, Ombrelloni, Bancomat in loco, Infermeria, Lavanderia self-service, Aria condizionata, Spiaggia privata, Servizio di pulizia, Cassaforte, Angolo cottura, Frigorifero, TV a schermo piatto, Bagno/doccia, Zona soggiorno, Piano cottura, Utensili da cucina, Camere per famiglie, </t>
         </is>
       </c>
@@ -521,6 +536,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>34 €</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Campo da tennis, Attività per bambini/famiglie, Miniclub, Wi-Fi, Piscina all'aperto, Ristorante, Bar in piscina, Bar a bordo piscina, Personale di intrattenimento, Intrattenimento serale, Ping pong, Giochi all'aperto per bambini, Animali domestici ammessi, Minimarket, Lavanderia self-service, Aria condizionata, Spiaggia privata, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Vista sull'oceano, </t>
         </is>
       </c>
@@ -546,6 +566,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>154 €</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Wi-Fi, Piscina, Bar/lounge, Noleggio di biciclette, Canoismo, Attività per bambini/famiglie, Miniclub, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Snack bar, Campo da tennis, Ping pong, Piscina per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Navetta o servizio taxi gratis, Area barbecue, Lounge/sala TV in comune, Terrazza solarium, Servizio lavanderia, Lavanderia self-service, Spiaggia privata, Angolo cottura, Frigorifero, TV a schermo piatto, Camere per famiglie, </t>
         </is>
       </c>
@@ -571,6 +596,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Ristorante, Spiaggia, Noleggio di biciclette, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Wi-Fi, Vasca idromassaggio, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Zona pranzo all'aperto, Snack bar, Aerobica, Freccette, Personale di intrattenimento, Intrattenimento serale, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Area barbecue, Minimarket, Hotel per non fumatori, Lounge/sala TV in comune, Lettini/sedie sdraio, Ombrelloni, Asciugatrice, Aria condizionata, Zona soggiorno, Divano, Appendiabiti, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Bagni privati, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Camere non fumatori, Camere per famiglie, </t>
         </is>
       </c>
@@ -591,10 +621,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ho trascorso 3 giorni in questa struttura in un villino in muratura. Ho trovato un ambiente pulito, personale gentilissimo e disponibile verso ogni richiesta. Bella piscina .in mezza pensio ne ho trovato cibo curato e con buona scelta.  La spiaggia è raggiungibile con una bella passeggiata, ma se non si vuole passeggiare la struttura offre una navetta. Lo stabilimento balneare convenzionato con la struttura è ottimo. Biciclette disponibili per percorrere una bella ciclabile sul mare,ideale anche per piacevoli passeggiate.</t>
+          <t>Ci siamo innamorati di questa struttura un anno fa, quando l'abbiamo scoperta per puro caso; e quest'anno, al momento di prenotare le vacanze, non abbiamo avuto dubbi: Garden River di nuovo. Per chi come noi ha un budget limitato e cerca una struttura comoda e ben organizzata, le casette in muratura sono a nostro avviso la scelta ideale. Ovvio che, trovandosi in un camping immerso nel verde (e nel profumo) dei tigli, non bisogna scandalizzarsi se di tanto in tanto la formica, l'insettino, il geco si affacciano nelle casette... ma le costruzioni sono pulite, essenziali nel loro arredo, comode, fresche e, cosa essenziale per una famiglia di cinque persone come la nostra, comodissime da pulire. Specialmente il bagno, con la doccia che prende l'intera parete e consente di entrare in due (lo scorso anno con la terza che era più piccolina questo dettaglio ci ha velocizzato non poco le operazioni di lavaggio😅), è funzionale nella sua estrema semplicità. Non aspettatevi il lusso, ma pulizia, concretezza e praticità. Per il resto, tutto funziona alla perfezione, come un ingranaggio ben oliato;  le macchinine dello staff si vedono costantemente girare per il camping per provvedere ad eventuali interventi/riparazioni; l'isola ecologica è ben organizzata e ben tenuta; non essendo noi "animali sociali" non abbiamo sfruttato l'animazione ma abbiamo molto apprezzato il fatto che  sia presente ma non  invadente; lo staff sempre sorridente e cordiale; tanti piccoli servizi per aiutare gli ospiti a rendere la loro vacanza più possibile perfetta. La ragazza al bar, giovanissima, sempre cordiale e sorridente. Insomma, si vede che, dietro le quinte c'è tanto, tanto lavoro di squadra.  Noi abbiamo optato per la spiagga libera di Pedaso, con acqua bassa e calma e sabbia, perfetta per bambini e mai affollata, ma volendo ci sono dei lidi in convenzione con servizio navetta. Insomma, una settimana di relax immersi nel verde. Non facciamo che consigliare il Garden River ad amici e conoscenti che cerchino un alloggio semplice ad un budget contenuto e che apprezzino la natura.  Per noi che abbiamo un'unica settimana di ferie a disposizione, veramente una coccola che ci rigenera.…</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Piscina, Bar/lounge, Noleggio di biciclette, Biciclette disponibili, Area giochi interna per bambini, Attività per bambini/famiglie, Internet, Piscina a sfioro, Piscina per adulti, Piscina all'aperto, Piscina piccola, Piscina recintata, Ristorante, Colazione disponibile, Freccette, Intrattenimento serale, Pesca, Karaoke, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Navetta o servizio taxi gratis, Servizio navetta, Hotel per non fumatori, Angolo cottura, Frigorifero, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
         </is>
@@ -621,6 +656,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>82 €</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Sala giochi, Parco giochi per bambini, Attività per bambini/famiglie, Parcheggio, Wi-Fi, Piscina all'aperto, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Escursioni, Campo da tennis, Tour in bicicletta, Intrattenimento serale, Ping pong, Tour a piedi, Parco acquatico esterno alla struttura, Scivolo acquatico, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Centro congressi con accesso a Internet, Strutture per conferenze, Sala banchetti, Sale riunioni, Concierge, Hotel per non fumatori, Arredi esterni, Lounge/sala TV in comune, Ombrelloni, Servizio lavanderia, Lavanderia self-service, Aria condizionata, Sala da pranzo, Servizio di pulizia, Balcone privato, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Cassaforte, Zona soggiorno, Sala da pranzo separata, Area soggiorno separata, Divano, Armadio/cabina, Appendiabiti, Bagni privati, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Bollitore elettrico, Utensili da cucina, Cabina doccia, Bagno/doccia, Asciugacapelli, Vista sulle montagne, Vista sull'oceano, Vista sulla piscina, Camere non fumatori, Suite, Camere per famiglie, </t>
         </is>
       </c>
@@ -646,6 +686,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>140 €</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Animali domestici ammessi, Angolo cottura, </t>
         </is>
       </c>
@@ -671,6 +716,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Caffetteria, Noleggio di biciclette, Aerobica, Servizio di babysitter, Parco giochi per bambini, Wi-Fi, Ristorante, Colazione disponibile, Pasti per bambini, Zona pranzo all'aperto, Freccette, Personale di intrattenimento, Intrattenimento serale, Pesca, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio taxi, Trattamenti per il viso, Massaggio completo, Manicure, Massaggio, Servizi di ceretta, Accesso diretto alle piste da sci, Sicurezza 24 ore su 24, Area barbecue, Concierge, Hotel per non fumatori, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Ombrello, Check-in/check-out express, Servizio lavanderia, Lavanderia self-service, Servizio stireria, Purificatore d'aria, Aria condizionata, Servizio di pulizia, Balcone privato, Bagni privati, Angolo cottura, TV satellitare/via cavo, Bidet, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Utensili da cucina, TV a schermo piatto, Cabina doccia, Asciugacapelli, Vista sulla piscina, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
         </is>
       </c>
@@ -696,6 +746,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Bar/lounge, Spiaggia, Noleggio di biciclette, Miniclub, Giochi all'aperto per bambini, Animali domestici ammessi, Parcheggio in strada, Ristorante, Pasti per bambini, Snack bar, Personale di intrattenimento, Intrattenimento serale, Ping pong, Servizio navetta, Area barbecue, Minimarket, Hotel per non fumatori, Servizio lavanderia, Aria condizionata, Spiaggia privata, Zona soggiorno, Acqua in bottiglia, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
         </is>
       </c>
@@ -719,7 +774,12 @@
           <t>Abbiamo affittato una delle casette. Posto raggiungibile agevolmente da Civitanova Alta seguendo Google Maps. La casa è dotata di tutto il necessario, potrete trovare una cucina funzionante con stoviglie già presenti. C’è l’aria condizionata. All’esterno una piscina rilassante ad uso privato di chi alloggia è un piccolo parco con giochi per bambini. Tutto molto rilassante. C’è il WiFi che funziona perfettamente e anche la possibilità di fare lavatrici se necessario. A noi Vodafone per chiamare non prendeva (forse altri operatori vanno bene) ma comunque si può usare la connessione per chiamare con Whatsapp.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -741,6 +801,11 @@
         </is>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>55 €</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Lezioni di yoga, Bar a bordo piscina, Spiaggia, Noleggio di biciclette, Attività per bambini/famiglie, Parcheggio custodito, Wi-Fi, Teli da piscina/mare, Piscina con vista, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Pasti per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio navetta, Sale riunioni, Area barbecue, Deposito bagagli, Hotel per non fumatori, Arredi esterni, Area picnic, Lettini/sedie sdraio, Terrazza solarium, Reception 24 ore su 24, Servizio lavanderia, Acqua in bottiglia, Angolo cottura, Camere per famiglie, </t>
         </is>

--- a/datasets/general_data_dataset_tripadvisor.xlsx
+++ b/datasets/general_data_dataset_tripadvisor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>facilities</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -476,12 +481,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>191 €</t>
+          <t>non disponibile</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Piscina, Lezioni di yoga, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Teli da piscina/mare, Piscina all'aperto, Corsi di fitness, Ristorante, Colazione a buffet, Drink di benvenuto omaggio, Noleggio di biciclette, Canoismo, Campo da tennis, Noleggi di attrezzature per sport acquatici, Windsurf, Tour in bicicletta, Personale di intrattenimento, Intrattenimento serale, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Servizio taxi, Sicurezza 24 ore su 24, Minimarket, Zanzariera, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Lavanderia self-service, Lavatrice, Camere insonorizzate, Aria condizionata, Spiaggia privata, Servizio di pulizia, Angolo cottura, TV a schermo piatto, Divano letto, Bidet, Cassaforte, Zona soggiorno, Divano, Armadio/cabina, Forno, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Asciugacapelli, Camere non fumatori, Camere per famiglie, </t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g1924689-d948494-Reviews-Natural_Village_Resort-Porto_Potenza_Picena_Potenza_Picena_Province_of_Macerata_Marche.html</t>
         </is>
       </c>
     </row>
@@ -514,6 +524,11 @@
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Wi-Fi, Giochi da piscina, Piscina all'aperto, Piscina con estremità bassa, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Bar in piscina, Noleggio di biciclette, Canoismo, Escursioni, Campo da tennis, Parco acquatico, Windsurf, Aerobica, Personale di intrattenimento, Intrattenimento serale, Ping pong, Scivolo acquatico, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Passeggini, Animali domestici ammessi, Area barbecue, Minimarket, Negozio di articoli da regalo, Quotidiano, Negozi, Lettini/sedie sdraio, Ombrelloni, Bancomat in loco, Infermeria, Lavanderia self-service, Aria condizionata, Spiaggia privata, Servizio di pulizia, Cassaforte, Angolo cottura, Frigorifero, TV a schermo piatto, Bagno/doccia, Zona soggiorno, Piano cottura, Utensili da cucina, Camere per famiglie, </t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g1582949-d2346767-Reviews-La_Risacca_Camping_Village_Formule_Hotel-Porto_Sant_Elpidio_Province_of_Fermo_Marche.html</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -536,12 +551,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>34 €</t>
+          <t>29 €</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Campo da tennis, Attività per bambini/famiglie, Miniclub, Wi-Fi, Piscina all'aperto, Ristorante, Bar in piscina, Bar a bordo piscina, Personale di intrattenimento, Intrattenimento serale, Ping pong, Giochi all'aperto per bambini, Animali domestici ammessi, Minimarket, Lavanderia self-service, Aria condizionata, Spiaggia privata, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Vista sull'oceano, </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g1741825-d1891906-Reviews-Girasole_Eco_Family_Village-Marina_Palmense_Fermo_Province_of_Fermo_Marche.html</t>
         </is>
       </c>
     </row>
@@ -566,12 +586,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>154 €</t>
+          <t>160 €</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Wi-Fi, Piscina, Bar/lounge, Noleggio di biciclette, Canoismo, Attività per bambini/famiglie, Miniclub, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Snack bar, Campo da tennis, Ping pong, Piscina per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Navetta o servizio taxi gratis, Area barbecue, Lounge/sala TV in comune, Terrazza solarium, Servizio lavanderia, Lavanderia self-service, Spiaggia privata, Angolo cottura, Frigorifero, TV a schermo piatto, Camere per famiglie, </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g608900-d1146098-Reviews-Green_Garden_Camping_Village-Sirolo_Province_of_Ancona_Marche.html</t>
         </is>
       </c>
     </row>
@@ -604,6 +629,11 @@
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Ristorante, Spiaggia, Noleggio di biciclette, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Wi-Fi, Vasca idromassaggio, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Zona pranzo all'aperto, Snack bar, Aerobica, Freccette, Personale di intrattenimento, Intrattenimento serale, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Area barbecue, Minimarket, Hotel per non fumatori, Lounge/sala TV in comune, Lettini/sedie sdraio, Ombrelloni, Asciugatrice, Aria condizionata, Zona soggiorno, Divano, Appendiabiti, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Bagni privati, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Camere non fumatori, Camere per famiglie, </t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g194914-d2344934-Reviews-Camping_Blu_Fantasy-Senigallia_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -621,7 +651,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ci siamo innamorati di questa struttura un anno fa, quando l'abbiamo scoperta per puro caso; e quest'anno, al momento di prenotare le vacanze, non abbiamo avuto dubbi: Garden River di nuovo. Per chi come noi ha un budget limitato e cerca una struttura comoda e ben organizzata, le casette in muratura sono a nostro avviso la scelta ideale. Ovvio che, trovandosi in un camping immerso nel verde (e nel profumo) dei tigli, non bisogna scandalizzarsi se di tanto in tanto la formica, l'insettino, il geco si affacciano nelle casette... ma le costruzioni sono pulite, essenziali nel loro arredo, comode, fresche e, cosa essenziale per una famiglia di cinque persone come la nostra, comodissime da pulire. Specialmente il bagno, con la doccia che prende l'intera parete e consente di entrare in due (lo scorso anno con la terza che era più piccolina questo dettaglio ci ha velocizzato non poco le operazioni di lavaggio😅), è funzionale nella sua estrema semplicità. Non aspettatevi il lusso, ma pulizia, concretezza e praticità. Per il resto, tutto funziona alla perfezione, come un ingranaggio ben oliato;  le macchinine dello staff si vedono costantemente girare per il camping per provvedere ad eventuali interventi/riparazioni; l'isola ecologica è ben organizzata e ben tenuta; non essendo noi "animali sociali" non abbiamo sfruttato l'animazione ma abbiamo molto apprezzato il fatto che  sia presente ma non  invadente; lo staff sempre sorridente e cordiale; tanti piccoli servizi per aiutare gli ospiti a rendere la loro vacanza più possibile perfetta. La ragazza al bar, giovanissima, sempre cordiale e sorridente. Insomma, si vede che, dietro le quinte c'è tanto, tanto lavoro di squadra.  Noi abbiamo optato per la spiagga libera di Pedaso, con acqua bassa e calma e sabbia, perfetta per bambini e mai affollata, ma volendo ci sono dei lidi in convenzione con servizio navetta. Insomma, una settimana di relax immersi nel verde. Non facciamo che consigliare il Garden River ad amici e conoscenti che cerchino un alloggio semplice ad un budget contenuto e che apprezzino la natura.  Per noi che abbiamo un'unica settimana di ferie a disposizione, veramente una coccola che ci rigenera.…</t>
+          <t>Abbiamo soggiornato x il ponte del 2 giugno, in un villino in muratura, pulito e funzionale. Ci siamo trovati benissimo. Il personale molto gentile e pronto a soddisfare qualsiasi richiesta. Al ristorante si mangiava benissimo e anche in questo caso, io che sono ciliaca e ho altre intolleranze alimentari, nn ho avuto nessun problema.  Il mare è poco distante e ci si arriva percorrendo una ciclopedonale, in alternativa il camping offre il servizio navetta.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -632,6 +662,11 @@
       <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Piscina, Bar/lounge, Noleggio di biciclette, Biciclette disponibili, Area giochi interna per bambini, Attività per bambini/famiglie, Internet, Piscina a sfioro, Piscina per adulti, Piscina all'aperto, Piscina piccola, Piscina recintata, Ristorante, Colazione disponibile, Freccette, Intrattenimento serale, Pesca, Karaoke, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Navetta o servizio taxi gratis, Servizio navetta, Hotel per non fumatori, Angolo cottura, Frigorifero, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g2189383-d4923901-Reviews-Centro_Vacanze_Garden_River-Altidona_Province_of_Fermo_Marche.html</t>
         </is>
       </c>
     </row>
@@ -656,12 +691,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82 €</t>
+          <t>89 €</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Sala giochi, Parco giochi per bambini, Attività per bambini/famiglie, Parcheggio, Wi-Fi, Piscina all'aperto, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Escursioni, Campo da tennis, Tour in bicicletta, Intrattenimento serale, Ping pong, Tour a piedi, Parco acquatico esterno alla struttura, Scivolo acquatico, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Centro congressi con accesso a Internet, Strutture per conferenze, Sala banchetti, Sale riunioni, Concierge, Hotel per non fumatori, Arredi esterni, Lounge/sala TV in comune, Ombrelloni, Servizio lavanderia, Lavanderia self-service, Aria condizionata, Sala da pranzo, Servizio di pulizia, Balcone privato, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Cassaforte, Zona soggiorno, Sala da pranzo separata, Area soggiorno separata, Divano, Armadio/cabina, Appendiabiti, Bagni privati, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Bollitore elettrico, Utensili da cucina, Cabina doccia, Bagno/doccia, Asciugacapelli, Vista sulle montagne, Vista sull'oceano, Vista sulla piscina, Camere non fumatori, Suite, Camere per famiglie, </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g2026765-d7082655-Reviews-Camping_Village_Mar_y_Sierra-San_Costanzo_Province_of_Pesaro_and_Urbino_Marche.html</t>
         </is>
       </c>
     </row>
@@ -694,6 +734,11 @@
           <t xml:space="preserve">Parcheggio gratuito, Animali domestici ammessi, Angolo cottura, </t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g2136886-d21340843-Reviews-Amapolas_Villaggio_Camping-Mombaroccio_Province_of_Pesaro_and_Urbino_Marche.html</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -724,6 +769,11 @@
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Caffetteria, Noleggio di biciclette, Aerobica, Servizio di babysitter, Parco giochi per bambini, Wi-Fi, Ristorante, Colazione disponibile, Pasti per bambini, Zona pranzo all'aperto, Freccette, Personale di intrattenimento, Intrattenimento serale, Pesca, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio taxi, Trattamenti per il viso, Massaggio completo, Manicure, Massaggio, Servizi di ceretta, Accesso diretto alle piste da sci, Sicurezza 24 ore su 24, Area barbecue, Concierge, Hotel per non fumatori, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Ombrello, Check-in/check-out express, Servizio lavanderia, Lavanderia self-service, Servizio stireria, Purificatore d'aria, Aria condizionata, Servizio di pulizia, Balcone privato, Bagni privati, Angolo cottura, TV satellitare/via cavo, Bidet, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Utensili da cucina, TV a schermo piatto, Cabina doccia, Asciugacapelli, Vista sulla piscina, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g1025201-d677045-Reviews-Villaggio_Turistico_Residence_Mare-Fermo_Province_of_Fermo_Marche.html</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -754,6 +804,11 @@
           <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Bar/lounge, Spiaggia, Noleggio di biciclette, Miniclub, Giochi all'aperto per bambini, Animali domestici ammessi, Parcheggio in strada, Ristorante, Pasti per bambini, Snack bar, Personale di intrattenimento, Intrattenimento serale, Ping pong, Servizio navetta, Area barbecue, Minimarket, Hotel per non fumatori, Servizio lavanderia, Aria condizionata, Spiaggia privata, Zona soggiorno, Acqua in bottiglia, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g194914-d3309922-Reviews-Camping_Villaggio_Cortina-Senigallia_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -780,6 +835,11 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g194742-d21379810-Reviews-Poggio_Imperiale_Marche-Civitanova_Marche_Province_of_Macerata_Marche.html</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -808,6 +868,501 @@
       <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Lezioni di yoga, Bar a bordo piscina, Spiaggia, Noleggio di biciclette, Attività per bambini/famiglie, Parcheggio custodito, Wi-Fi, Teli da piscina/mare, Piscina con vista, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Pasti per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio navetta, Sale riunioni, Area barbecue, Deposito bagagli, Hotel per non fumatori, Arredi esterni, Area picnic, Lettini/sedie sdraio, Terrazza solarium, Reception 24 ore su 24, Servizio lavanderia, Acqua in bottiglia, Angolo cottura, Camere per famiglie, </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.it/Hotel_Review-g23906399-d12336250-Reviews-Casale_Civetta-Borgo_della_Consolazione_Trecastelli_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La Mimosa Camping</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Strada Nazionale Adriatica Sud 259, 61032, Fano Italy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>We had booked a holiday cottage to attend a family wedding in the local area. We were so happy that we chose La Mimosa. Our Italian language is not good but they went out of the way to make us feel welcome and looked after.   The chalet was modern, clean, neat and tidy, exactly as advertised. There were basic kitchen utensils to use and the small shop at reception is very convenient. The Chalet is small but functional, perfect for a seaside holiday.  This is a family run business and everybody went out of their way to see that we were welcome and looked after. The seafood restaurant was also excellent.  The beach is easy to get to and ideal for smaller children as there is loads of sand to play on and the water is very shallow. The sun loungers that come with the accommodation booking are lovely to use. Throughout the visit we felt safe and secure.  We found a large supermarket about 6 km (heading south) down the road for more supplies.   I would certainly go there again and have already recommended it to other family members with children.…</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Internet, Outdoor pool, Restaurant, Poolside bar, Convenience store, Air conditioning, Private beach, Kitchenette, </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g194759-d4026529-Reviews-La_Mimosa_Camping-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camping Vettore</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Strada Per San Nicola 15, 63094, Montegallo Italy</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>This is the best camping that I have ever been to in my entire life! This is absolute fantastic place to be with Your tent. The lovely scenery and quiet enviorement is just welcoming here and making You want to stay there for days! A tent-perfect-place to stay: green clean grass, good showers and bath facilities. The village is very close with two shops, couple restourants and cafes. The mountain trails are very close so this is the ultimate camping site in Apennines. Very quiet and cheap.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Restaurant, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g2002511-d2318786-Reviews-Camping_Vettore-Montegallo_Province_of_Ascoli_Piceno_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camping Monte Prata</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Localita Schianceto SNC, 62039, Castelsantangelo sul Nera Italy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Spacious pitches, lots of shade, remote pitches where you can enjoy the silence and the sounds of nature. The location is beautiful, we have heard wolves, boar, owls, hawks and an eagle, seen squirrels and a wild cat all from our pitch. During our visit two staff members played acoustic guitar(rock) from time to time, for us it really added to the atmosphere. The staff is friendly and helpful, there is a really nice bar-market(though a bit small).  The price is good. The sanitary is a bit outdated, but it works.  The nearest supermarket is ca. 35mins drive away in Borgo Ceretto(Eurospin franchise). The camping lays at +1200 m above sealevel, this means it can get a bit cold after sundown(I only brought one sweater, really should've brought more).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pets Allowed ( Dog / Pet Friendly ), </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g1566582-d3310023-Reviews-Camping_Monte_Prata-Castelsantangelo_sul_Nera_Province_of_Macerata_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Camping Centro Turistico Belvedere</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Montecucco 19, 62012, Civitanova Marche Italy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Camping Centro Turistico Belvedere is located in Civitanova Marche, at less than 1 km from the sea. Placed on the top of a hill completely covered by a pine forest, it offers a beautiful panorama from Monte Conero to San Benedetto. Camping places are completely shady; you can also rent caravans or bungalows. Moreover, Camping Belvedere offers two swimming pools, a coffee bar, a restaurant and a pizzeria. Dogs and other pets welcome!</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Pool, Bar / lounge, Restaurant, Breakfast available, Tennis court, Pets Allowed ( Dog / Pet Friendly ), Self-serve laundry, Refrigerator, </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g194742-d1993072-Reviews-Camping_Centro_Turistico_Belvedere-Civitanova_Marche_Province_of_Macerata_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Camping Stella Maris</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Via Ammiraglio Cappellini 5, 61032, Fano Italy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Super camping. Evwrything is relaxed. Very nice beach and perfect swimmingpool. The son of the owner is the sweetest person in the world. He suprised us with a pick up with a very nice car to bring us to an excellent restaurant. If you look for a perfect camping this is the one!</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Restaurant, Swimup bar, Kitchenette, </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g194759-d6603161-Reviews-Camping_Stella_Maris-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Conero Azzurro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Via Castelfidardo 80, 60026 Numana Italy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Villaggio immerso nel verde, con cottage, chalet e bungalow indipendenti. Situato in prima fila mare, con ampia spiaggia privata e accesso diretto tramite un comodo sottopasso. Ideale per famiglie con bambini.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Bicycle rental, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Plunge pool, Restaurant, Breakfast available, Kids' meals, Snack bar, Swimup bar, Tennis court, Entertainment staff, Table tennis, Kids' outdoor play equipment, Conference facilities, Banquet room, Meeting rooms, Convenience store, Gift shop, Sun umbrellas, Self-serve laundry, Air conditioning, Private beach, Safe, Kitchenette, Refrigerator, Non-smoking rooms, Family rooms, </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g194838-d676423-Reviews-Conero_Azzurro-Numana_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camping Don Diego</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lungomare Alcide De' Gasperi 128, 63066 Grottammare Italy</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Village and Camping on the sea of the Riviera of the Palms, in the Region Marche, central Italy, adriatic coast. Bungalows in masonry and pitche for camping open air, at 10 mt from the sea by shallow water and fine sand. Clean sea by European Blue Flag.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Business Center with Internet Access, Self-serve laundry, Wifi, Restaurant, Kitchenette, </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g730082-d1548649-Reviews-Camping_Don_Diego-Grottammare_Province_of_Ascoli_Piceno_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Camping Lpre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti 45, 60010 Ostra Italy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Campeggio nella campagna dell'entroterra marchigiano (tra i caselli autostradali di Senigallia e Montemarciano-15/20 min.) situato in borgo tranquillo e caratteristico. Piazzole ampie e ombreggiate da ulivi, servizi igienici pulitissimi. Titolare (e fidanzata) molto gentili e accoglienti. Ottima copertura wifi gratuito in tutta la struttura. Torneremo presto a trovarvi: complimenti e grazie di tutto!!</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free High Speed Internet (WiFi), Wifi, Pets Allowed ( Dog / Pet Friendly ), </t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g2140648-d3519310-Reviews-Camping_Lpre-Ostra_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Camping Paradiso</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Via Rive del Faro 2, 61121, Pesaro Italy</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We stayed here in a Tendi tent for a week. Camping is nice, not too big. Beautiful scenery and shady places. Suitable for smaller children.   Pool has very strict rules, which we found very patronizing.   Small shop available,  bread every morning which was great!   </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Pool, Bar / lounge, Restaurant, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Self-serve laundry, Seating area, Sofa, Kitchenette, Refrigerator, Kitchenware, </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g187796-d4116318-Reviews-Camping_Paradiso-Pesaro_Province_of_Pesaro_and_Urbino_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Camping Bellamare</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Viale Scarfiotti 13, 62017 Porto Recanati Italy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The Bellamare Camping is immersed in the enchanting Conero Riviera covering an area of 50,000 sq mt. It is the perfect starting point for excursions and visits to places of major touristic interest in the Marche. The Camping Bellamare is directly by the beach of Porto Recanati far away from the railway, which is quite an exceptional location along the Adriatic coast of Marche. The campsite offers various types of accommodations such as pleasant bungalows, beachfront apartments and finely curated lown grass pitches each one surrounded by trees. The entetainment team of the campsite organizes fun activities, games, kids club, evening shows, sports for adults and kids. Porto Recanati is an oasis of peace and tranquility in the beautiful scenery of Mount Conero, the ideal place for your holiday in the Marche.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Fitness classes, Bar / lounge, Beach, Bicycle rental, Children's playground, Wifi, Paid wifi, Adult pool, Outdoor pool, Plunge pool, Shallow end in pool, Coffee shop, Restaurant, Breakfast available, Outdoor dining area, Snack bar, Wine / champagne, Swimup bar, Poolside bar, Game room, Hiking, Aerobics, Entertainment staff, Evening entertainment, Indoor play area for children, Children Activities (Kid / Family Friendly), Kids club, Kids' outdoor play equipment, Highchairs available, Concierge, Convenience store, Sun deck, Sun loungers / beach chairs, Sun terrace, Sun umbrellas, Infirmary, Express check-in / check-out, Clothes dryer, Laundry service, Self-serve laundry, Washing machine, Allergy-free room, Air conditioning, Dining area, Housekeeping, Clothes rack, Microwave, Stovetop, Walk-in shower, Kitchenware, Hair dryer, Family rooms, </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g194858-d1815916-Reviews-Camping_Bellamare-Porto_Recanati_Province_of_Macerata_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Camping Reno</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Via Moricone 7, 60020 Sirolo Italy</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The location of this campsite is excellent, although on a steep hill, it is possible to walk into the centre of the beautiful town in 10 minutes.   The campsite is very basic with fairly poor, unrenovated sanitaire.  Staff are very pleasant and helpful.  Sirolo is worth a visit, and has great views over the sea.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bar / lounge, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g608900-d4817085-Reviews-Camping_Reno-Sirolo_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camping Summerland</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Via Francesco Podesti 236, 60019, Senigallia Italy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The Camping Holiday Center Summerland rises in a quiet and shady area within the residential zone of Senigallia. The so-called "Spiaggia di Velluto" (“Velvet beach”), famous for its wonderful sandy beach, is only 150 m. far from the camping. It’s the ideal place for children because of the knee-deep water; tourists can choose between free beach (free access) or private beach (with beach facilities on charge). The camping extends on a 45.000 square meters area of grassy ground and has: 176 little squares, 89 bungalows, 10 chalets, 3 restrooms located in different areas with free hot water in showers and washbasins (no coins!!!), two inside parking places and an outside one. Our strong points are the green areas, 3 swimming pools with solarium and sports facilities (soccer and volley grounds, tennis court) all free-access. A friendly staff will welcome you at the camping. We work for families from more than 40 years; for that reason we can satisfy both adults and children needs.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Tennis court, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Restaurant, Evening entertainment, Kids' outdoor play equipment, Pets Allowed ( Dog / Pet Friendly ), Concierge, Convenience store, Laundry service, Self-serve laundry, Air conditioning, Kitchenette, Microwave, Refrigerator, Family rooms, </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g194914-d2316135-Reviews-Camping_Summerland-Senigallia_Province_of_Ancona_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Camping Gabicce Monte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Via Panoramica 148, 61011 Gabicce Monte Italy</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Camping Gabicce Monte is a small and intimate camp, surrounded by the San Bartolo natural park. A cool and shaded terrace overlooking the sea from which to enjoy a beautiful landscape. Located halfway between the sea and Gabicce Vallugola, Camping Gabicce Monte is perfect for lovers of hiking or biking. The beaches of Gabicce and Cattolica are easily reachable on foot in 15 minutes through scenic trails. The bay cobbled below the campground is instead reached in about ten minutes through a path in the wild and enchanting forest. From the rooftop terrace of Gabicce Monte, just 500 meters from the campsite, there are buses and shuttles every half hour to the beaches. Finally, for the very young or the nightlife lovers, the campsite is just a few minutes by car or on foot from bar and pubs of Gabicce and Cattolica and one of the most famous discos of the Riviera: the Baia Imperiale.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Wifi, Breakfast available, Pets Allowed ( Dog / Pet Friendly ), BBQ facilities, Concierge, Self-serve laundry, Non-smoking hotel, Air conditioning, Kitchenette, Refrigerator, Ocean view, Non-smoking rooms, Family rooms, </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g2275905-d2250335-Reviews-Camping_Gabicce_Monte-Gabicce_Monte_Province_of_Pesaro_and_Urbino_Marche.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Camping Club Internazionale</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Via San Michele 10, 60020 Sirolo Italy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>The site is beautiful, servise is nice, food is good in restaurant, good choice in the shop, clean bathrooms, short walk to the beach and downtown. While the quite hours are respected within the camping itself it is of no use at all, because of the noise from Sirolo till late night. Everynight. Is like your tent is placed in some bar. Was tired everyday we stayed in the camping. This canceled all the good points the camping offers, i did not enjoy my stay at all and do not advice for anyone who cant sleep in noisy places.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>non disponibile</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Bicycle rental, Table tennis, Books, DVDs, music for children, Children Activities (Kid / Family Friendly), Wifi, Paid wifi, Outdoor pool, Shallow end in pool, Fence around pool, Restaurant, Special diet menus, Vending machine, Tennis court offsite, Kids club, Kids' outdoor play equipment, BBQ facilities, Concierge, Convenience store, Newspaper, Outdoor furniture, Picnic area, Sun loungers / beach chairs, Sun terrace, Self-serve laundry, Ocean view, </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>
         </is>
       </c>
     </row>

--- a/datasets/general_data_dataset_tripadvisor.xlsx
+++ b/datasets/general_data_dataset_tripadvisor.xlsx
@@ -464,15 +464,31 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Natural Village Resort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Strada Statale 16, Km. 331,48 Contrada Torrenova, 62018 Porto Potenza Picena, Potenza Picena Italia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Il Natural Village Resort è un prestigioso villaggio turistico della Riviera Adriatica a due passi della Riviera del Conero, a Potenza Picena nelle Marche. Si estende per 6 ettari ed è composto da 245 chalet in legno immersi nel verde. Si affaccia direttamente sul mare Bandiera Blu, con spiaggia privata ed attrezzata con lettini ed ombrelloni. A poca distanza da Porto Recanati e dalle principali località di Portonovo, Sirolo, Numana, Marcelli e la bellissima città di Ancona, il Natural Village Resort è un vero paradiso per chi ama il mare, il relax, lo sport e la natura. Non perdere l’opportunità di vivere una vacanza indimenticabile in famiglia, in coppia e con gli amici. I vostri amici a 4 zampe sono i benvenuti al Natural Village Resort. I bellissimi chalet del Natural Village Resort sono molto confortevoli, sono in legno dipinto con pitture assolutamente ecologiche e l’intero villaggio è costruito a bassa cementificazione nel totale rispetto dell’ambiente. Gli chalet si armonizzano con il paesaggio circostante, arricchendolo. In più: tre bar, due ristoranti, il mini-market, la pizzeria &amp; Take Away, il campetto polivalente per calcio e tennis, noleggio biciclette e numerose aree giochi attrezzate per bambini. L’animazione presente organizza ogni giorno tante attività divertenti e coinvolgenti per gli ospiti, grandi e piccoli: giochi, tornei, spettacoli… Internet wireless per tutto il villaggio.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Piscina, Lezioni di yoga, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Teli da piscina/mare, Piscina all'aperto, Corsi di fitness, Ristorante, Colazione a buffet, Drink di benvenuto omaggio, Noleggio di biciclette, Canoismo, Campo da tennis, Noleggi di attrezzature per sport acquatici, Windsurf, Tour in bicicletta, Personale di intrattenimento, Intrattenimento serale, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Servizio taxi, Sicurezza 24 ore su 24, Minimarket, Zanzariera, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Lavanderia self-service, Lavatrice, Camere insonorizzate, Aria condizionata, Spiaggia privata, Servizio di pulizia, Angolo cottura, TV a schermo piatto, Divano letto, Bidet, Cassaforte, Zona soggiorno, Divano, Armadio/cabina, Forno, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Asciugacapelli, Camere non fumatori, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g1924689-d948494-Reviews-Natural_Village_Resort-Porto_Potenza_Picena_Potenza_Picena_Province_of_Macerata_Marche.html</t>
@@ -483,15 +499,31 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>La Risacca Camping Village - Formule Hotel</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Via Europa 100, 63821 Porto Sant'Elpidio Italia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Il nostro ristorante è all'interno di La Risacca Family Camping Village, situato a lato della Piazza, dove si svolgono tutte le attività di animazione e intrattenimento serale. Lambiente marinaro del ristorante è intimo, cordiale e accogliente, vi si respira una fresca atmosfera familiare. Dispone di una ampia sala interna climatizzata e di tavoli all'esterno sotto un porticato e in una terrazza attrezzata. Il nostro ristorante è affiliato AIC (Associazione Italiana Celiachia) ed è possibile mangiare senza glutine in tutta sicurezza. Il menù è stato studiato per accontentare i gusti di una tipica famiglia italiana: carne, pesce, pizza, specialità della zona.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>non disponibile</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>275 €</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Wi-Fi, Giochi da piscina, Piscina all'aperto, Piscina con estremità bassa, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Bar in piscina, Noleggio di biciclette, Canoismo, Escursioni, Campo da tennis, Parco acquatico, Windsurf, Aerobica, Personale di intrattenimento, Intrattenimento serale, Ping pong, Scivolo acquatico, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Passeggini, Animali domestici ammessi, Area barbecue, Minimarket, Negozio di articoli da regalo, Quotidiano, Negozi, Lettini/sedie sdraio, Ombrelloni, Bancomat in loco, Infermeria, Lavanderia self-service, Aria condizionata, Spiaggia privata, Servizio di pulizia, Cassaforte, Angolo cottura, Frigorifero, TV a schermo piatto, Bagno/doccia, Zona soggiorno, Piano cottura, Utensili da cucina, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g1582949-d2346767-Reviews-La_Risacca_Camping_Village_Formule_Hotel-Porto_Sant_Elpidio_Province_of_Fermo_Marche.html</t>
@@ -502,15 +534,31 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Girasole Eco Family Village</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Via Marina Palmense, 63900 Marina Palmense, Fermo Italia</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Complesso ricettivo direttamente sul mare, immerso in una vegetazione rigogliosa, in cui troverete spaziosi chalet in legno e confortevoli case mobili, acquapark con piscina e scivolo e vasche idromassaggio, spiaggia attrezzata, ristorante-bar, supermercato, parco giochi e tanti servizi per una vacanza di divertimento e relax.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>non disponibile</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>29 €</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Campo da tennis, Attività per bambini/famiglie, Miniclub, Wi-Fi, Piscina all'aperto, Ristorante, Bar in piscina, Bar a bordo piscina, Personale di intrattenimento, Intrattenimento serale, Ping pong, Giochi all'aperto per bambini, Animali domestici ammessi, Minimarket, Lavanderia self-service, Aria condizionata, Spiaggia privata, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Vista sull'oceano, </t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g1741825-d1891906-Reviews-Girasole_Eco_Family_Village-Marina_Palmense_Fermo_Province_of_Fermo_Marche.html</t>
@@ -521,15 +569,31 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Green Garden Camping Village</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Via Peschiera, 3, 60020 Sirolo Italia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Buon campeggio per famiglie o per chi cerca in un luogo tranquillo. Abbiamo preso una casa mobile standard (2 adulti e 2 ragazze) e ci siamo trovati bene, anche con la gestione degli spazi. La casa mobile e' dotata di tutto il necessario. È un po' "dondolante", ma niente di insopportabile. Campeggio immerso nella natura e piacevolmente ventilato. Vicino al centro di Sirolo e a Numana per piacevoli passeggiate serali. Ottimo servizio navetta per spiaggia convenzionata (ombrellone e due lettini compresi nel prezzo). Abbiamo apprezzato anche la piscina come ristoro dopo le belle camminate sul Conero. Nel ristorante del campeggio abbiamo gustato un'ottima pizza a lunga lievitazione che consigliamo vivamente e una buona frittura di pesce.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>non disponibile</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>160 €</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Wi-Fi, Piscina, Bar/lounge, Noleggio di biciclette, Canoismo, Attività per bambini/famiglie, Miniclub, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Snack bar, Campo da tennis, Ping pong, Piscina per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Navetta o servizio taxi gratis, Area barbecue, Lounge/sala TV in comune, Terrazza solarium, Servizio lavanderia, Lavanderia self-service, Spiaggia privata, Angolo cottura, Frigorifero, TV a schermo piatto, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g608900-d1146098-Reviews-Green_Garden_Camping_Village-Sirolo_Province_of_Ancona_Marche.html</t>
@@ -540,15 +604,31 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Camping Blu Fantasy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lungomare Italia 3/b, 60019, Senigallia Italia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 	La vacanza al Camping Blu è all'insegna del comfort e del relax.Al Camping Blu sono disponibili piazzole ombreggiate e spaziose per tende, camper e caravan a pochi metri dal mare.A disposizione degli ospiti anche moderne case mobili climatizzate, confortevoli appartamenti, piscine, parco giochi e campo da beach volley.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Ristorante, Spiaggia, Noleggio di biciclette, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Wi-Fi, Vasca idromassaggio, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Zona pranzo all'aperto, Snack bar, Aerobica, Freccette, Personale di intrattenimento, Intrattenimento serale, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Area barbecue, Minimarket, Hotel per non fumatori, Lounge/sala TV in comune, Lettini/sedie sdraio, Ombrelloni, Asciugatrice, Aria condizionata, Zona soggiorno, Divano, Appendiabiti, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Bagni privati, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Camere non fumatori, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g194914-d2344934-Reviews-Camping_Blu_Fantasy-Senigallia_Province_of_Ancona_Marche.html</t>
@@ -559,15 +639,31 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Centro Vacanze Garden River</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Via Ottorino Respighi snc, 63824 Altidona Italia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Abbiamo soggiornato x il ponte del 2 giugno, in un villino in muratura, pulito e funzionale. Ci siamo trovati benissimo. Il personale molto gentile e pronto a soddisfare qualsiasi richiesta. Al ristorante si mangiava benissimo e anche in questo caso, io che sono ciliaca e ho altre intolleranze alimentari, nn ho avuto nessun problema.  Il mare è poco distante e ci si arriva percorrendo una ciclopedonale, in alternativa il camping offre il servizio navetta.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Piscina, Bar/lounge, Noleggio di biciclette, Biciclette disponibili, Area giochi interna per bambini, Attività per bambini/famiglie, Internet, Piscina a sfioro, Piscina per adulti, Piscina all'aperto, Piscina piccola, Piscina recintata, Ristorante, Colazione disponibile, Freccette, Intrattenimento serale, Pesca, Karaoke, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Navetta o servizio taxi gratis, Servizio navetta, Hotel per non fumatori, Angolo cottura, Frigorifero, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g2189383-d4923901-Reviews-Centro_Vacanze_Garden_River-Altidona_Province_of_Fermo_Marche.html</t>
@@ -578,15 +674,31 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camping Village Mar y Sierra</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Strada San Gervasio 3 Frazione Stacciola, 61039, San Costanzo Italia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Posto super accogliente con cibo di ottima qualità e abbondante! Il personale di una gentilezza e disponibilità mai vista prima.  Per un diciottesimo ha superato le aspettative!! Da tornarci sicuramente</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non disponibile</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>89 €</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Sala giochi, Parco giochi per bambini, Attività per bambini/famiglie, Parcheggio, Wi-Fi, Piscina all'aperto, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Escursioni, Campo da tennis, Tour in bicicletta, Intrattenimento serale, Ping pong, Tour a piedi, Parco acquatico esterno alla struttura, Scivolo acquatico, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Centro congressi con accesso a Internet, Strutture per conferenze, Sala banchetti, Sale riunioni, Concierge, Hotel per non fumatori, Arredi esterni, Lounge/sala TV in comune, Ombrelloni, Servizio lavanderia, Lavanderia self-service, Aria condizionata, Sala da pranzo, Servizio di pulizia, Balcone privato, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Cassaforte, Zona soggiorno, Sala da pranzo separata, Area soggiorno separata, Divano, Armadio/cabina, Appendiabiti, Bagni privati, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Bollitore elettrico, Utensili da cucina, Cabina doccia, Bagno/doccia, Asciugacapelli, Vista sulle montagne, Vista sull'oceano, Vista sulla piscina, Camere non fumatori, Suite, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g2026765-d7082655-Reviews-Camping_Village_Mar_y_Sierra-San_Costanzo_Province_of_Pesaro_and_Urbino_Marche.html</t>
@@ -597,15 +709,31 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Amapolas Villaggio &amp; Camping</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>225 Via Villagrande, 61024 Mombaroccio Italia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Amapolas Villaggio è situato tra le dolci colline di Villagrande di Mombaroccio, punto di partenza ideale per vivere i sapori e i colori delle Marche. A disposizione dei nostri ospiti casette mobili di diverse dimensioni in cui soggiornare nel comfort più totale: dotate di cucina attrezzata, bagno con doccia, aria condizionata e patio con vista sul paesaggio rurale.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non disponibile</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>140 €</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Animali domestici ammessi, Angolo cottura, </t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g2136886-d21340843-Reviews-Amapolas_Villaggio_Camping-Mombaroccio_Province_of_Pesaro_and_Urbino_Marche.html</t>
@@ -616,15 +744,31 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Residence Mare</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Via Ugo La Malfa 19 Località Lido San Tommaso, 63900, Fermo Italia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Il Villaggio Turistico Residence Mare si trova nel centro abitato di Lido San Tommaso sul lungomare nord di Fermo ed è un luogo ideale per famiglie con bambini e coppie poichè è tranquillo, essendo di piccole dimensioni e senza il frastuono stradale o ferroviario. Si trova sulla spiaggia libera alla quale si accede direttamente (senza alcun costo d'ingresso), composta di sabbia e ghiaia.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Caffetteria, Noleggio di biciclette, Aerobica, Servizio di babysitter, Parco giochi per bambini, Wi-Fi, Ristorante, Colazione disponibile, Pasti per bambini, Zona pranzo all'aperto, Freccette, Personale di intrattenimento, Intrattenimento serale, Pesca, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio taxi, Trattamenti per il viso, Massaggio completo, Manicure, Massaggio, Servizi di ceretta, Accesso diretto alle piste da sci, Sicurezza 24 ore su 24, Area barbecue, Concierge, Hotel per non fumatori, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Ombrello, Check-in/check-out express, Servizio lavanderia, Lavanderia self-service, Servizio stireria, Purificatore d'aria, Aria condizionata, Servizio di pulizia, Balcone privato, Bagni privati, Angolo cottura, TV satellitare/via cavo, Bidet, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Utensili da cucina, TV a schermo piatto, Cabina doccia, Asciugacapelli, Vista sulla piscina, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g1025201-d677045-Reviews-Villaggio_Turistico_Residence_Mare-Fermo_Province_of_Fermo_Marche.html</t>
@@ -635,15 +779,31 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Camping Villaggio Cortina</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lungomare Italia 1/1, 60019, Senigallia Italia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sono stata in vacanza in questo camping due settimane a settembre, ho dovuto cambiare mobilhouse perché entrava acqua dentro durante le giornate di pioggia, dopo aver chiesto di poter cambiare mobilhouse ho dovuto Pagare 50 euro per pulizie per la mobilhouse successiva. Campeggio sporco, mi chiedo come mai l’asl non intervenga, oltretutto nel prima mobilhouse al nostro arrivo entrando abbiamo sentito in forte odore di muffa.  I giardini delle mobilhouse sono inesistenti e non sono curati nel modo giusto per il prezzo richiesto, il bar pochissima cibo da mangiare e Sporco, la Ciotola per i cani è sporca e verde nonostante la nostra richiesta di pulirla. Mi chiedo ma come fanno a continuare a lavorare.... dopo la pandemia che c’è stata quest’anno.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Bar/lounge, Spiaggia, Noleggio di biciclette, Miniclub, Giochi all'aperto per bambini, Animali domestici ammessi, Parcheggio in strada, Ristorante, Pasti per bambini, Snack bar, Personale di intrattenimento, Intrattenimento serale, Ping pong, Servizio navetta, Area barbecue, Minimarket, Hotel per non fumatori, Servizio lavanderia, Aria condizionata, Spiaggia privata, Zona soggiorno, Acqua in bottiglia, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g194914-d3309922-Reviews-Camping_Villaggio_Cortina-Senigallia_Province_of_Ancona_Marche.html</t>
@@ -654,9 +814,21 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Poggio Imperiale Marche</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>18 Contrada San Savino, 62012, Civitanova Marche Italia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Abbiamo affittato una delle casette. Posto raggiungibile agevolmente da Civitanova Alta seguendo Google Maps. La casa è dotata di tutto il necessario, potrete trovare una cucina funzionante con stoviglie già presenti. C’è l’aria condizionata. All’esterno una piscina rilassante ad uso privato di chi alloggia è un piccolo parco con giochi per bambini. Tutto molto rilassante. C’è il WiFi che funziona perfettamente e anche la possibilità di fare lavatrici se necessario. A noi Vodafone per chiamare non prendeva (forse altri operatori vanno bene) ma comunque si può usare la connessione per chiamare con Whatsapp.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>non disponibile</t>
@@ -673,15 +845,31 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Casale Civetta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Via Consolazione 20, 60012 Borgo della Consolazione, Trecastelli Italia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Casale Civetta ha un parco alberato con sentieri per passeggiate interne interrotte da tavoli in pietra. Ampi spazi aperti, pavimentati con mattoni dove camminare a piedi nudi.Una piscina panoramica sulle colline.Un laboratorio di scultura del tufo.Alberi da frutto. Animali in libertà, pesci, gatti e galline. Amicizia, familiarità,semplicità,arte,accoglienza e condivisione della propria umanità.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non disponibile</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>55 €</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Lezioni di yoga, Bar a bordo piscina, Spiaggia, Noleggio di biciclette, Attività per bambini/famiglie, Parcheggio custodito, Wi-Fi, Teli da piscina/mare, Piscina con vista, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Pasti per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio navetta, Sale riunioni, Area barbecue, Deposito bagagli, Hotel per non fumatori, Arredi esterni, Area picnic, Lettini/sedie sdraio, Terrazza solarium, Reception 24 ore su 24, Servizio lavanderia, Acqua in bottiglia, Angolo cottura, Camere per famiglie, </t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.it/Hotel_Review-g23906399-d12336250-Reviews-Casale_Civetta-Borgo_della_Consolazione_Trecastelli_Province_of_Ancona_Marche.html</t>
@@ -692,15 +880,31 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>La Mimosa Camping</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Strada Nazionale Adriatica Sud 259, 61032, Fano Italy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>We had booked a holiday cottage to attend a family wedding in the local area. We were so happy that we chose La Mimosa. Our Italian language is not good but they went out of the way to make us feel welcome and looked after.   The chalet was modern, clean, neat and tidy, exactly as advertised. There were basic kitchen utensils to use and the small shop at reception is very convenient. The Chalet is small but functional, perfect for a seaside holiday.  This is a family run business and everybody went out of their way to see that we were welcome and looked after. The seafood restaurant was also excellent.  The beach is easy to get to and ideal for smaller children as there is loads of sand to play on and the water is very shallow. The sun loungers that come with the accommodation booking are lovely to use. Throughout the visit we felt safe and secure.  We found a large supermarket about 6 km (heading south) down the road for more supplies.   I would certainly go there again and have already recommended it to other family members with children.…</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Internet, Outdoor pool, Restaurant, Poolside bar, Convenience store, Air conditioning, Private beach, Kitchenette, </t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g194759-d4026529-Reviews-La_Mimosa_Camping-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
@@ -711,15 +915,31 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camping Vettore</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Strada Per San Nicola 15, 63094, Montegallo Italy</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>This is the best camping that I have ever been to in my entire life! This is absolute fantastic place to be with Your tent. The lovely scenery and quiet enviorement is just welcoming here and making You want to stay there for days! A tent-perfect-place to stay: green clean grass, good showers and bath facilities. The village is very close with two shops, couple restourants and cafes. The mountain trails are very close so this is the ultimate camping site in Apennines. Very quiet and cheap.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Restaurant, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g2002511-d2318786-Reviews-Camping_Vettore-Montegallo_Province_of_Ascoli_Piceno_Marche.html</t>
@@ -730,15 +950,31 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camping Monte Prata</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Localita Schianceto SNC, 62039, Castelsantangelo sul Nera Italy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Spacious pitches, lots of shade, remote pitches where you can enjoy the silence and the sounds of nature. The location is beautiful, we have heard wolves, boar, owls, hawks and an eagle, seen squirrels and a wild cat all from our pitch. During our visit two staff members played acoustic guitar(rock) from time to time, for us it really added to the atmosphere. The staff is friendly and helpful, there is a really nice bar-market(though a bit small).  The price is good. The sanitary is a bit outdated, but it works.  The nearest supermarket is ca. 35mins drive away in Borgo Ceretto(Eurospin franchise). The camping lays at +1200 m above sealevel, this means it can get a bit cold after sundown(I only brought one sweater, really should've brought more).</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pets Allowed ( Dog / Pet Friendly ), </t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g1566582-d3310023-Reviews-Camping_Monte_Prata-Castelsantangelo_sul_Nera_Province_of_Macerata_Marche.html</t>
@@ -749,15 +985,31 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Camping Centro Turistico Belvedere</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Montecucco 19, 62012, Civitanova Marche Italy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Camping Centro Turistico Belvedere is located in Civitanova Marche, at less than 1 km from the sea. Placed on the top of a hill completely covered by a pine forest, it offers a beautiful panorama from Monte Conero to San Benedetto. Camping places are completely shady; you can also rent caravans or bungalows. Moreover, Camping Belvedere offers two swimming pools, a coffee bar, a restaurant and a pizzeria. Dogs and other pets welcome!</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Pool, Bar / lounge, Restaurant, Breakfast available, Tennis court, Pets Allowed ( Dog / Pet Friendly ), Self-serve laundry, Refrigerator, </t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g194742-d1993072-Reviews-Camping_Centro_Turistico_Belvedere-Civitanova_Marche_Province_of_Macerata_Marche.html</t>
@@ -768,15 +1020,31 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Camping Stella Maris</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Via Ammiraglio Cappellini 5, 61032, Fano Italy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Super camping. Evwrything is relaxed. Very nice beach and perfect swimmingpool. The son of the owner is the sweetest person in the world. He suprised us with a pick up with a very nice car to bring us to an excellent restaurant. If you look for a perfect camping this is the one!</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Restaurant, Swimup bar, Kitchenette, </t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g194759-d6603161-Reviews-Camping_Stella_Maris-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
@@ -787,15 +1055,31 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Conero Azzurro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Via Castelfidardo 80, 60026 Numana Italy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Villaggio immerso nel verde, con cottage, chalet e bungalow indipendenti. Situato in prima fila mare, con ampia spiaggia privata e accesso diretto tramite un comodo sottopasso. Ideale per famiglie con bambini.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Bicycle rental, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Plunge pool, Restaurant, Breakfast available, Kids' meals, Snack bar, Swimup bar, Tennis court, Entertainment staff, Table tennis, Kids' outdoor play equipment, Conference facilities, Banquet room, Meeting rooms, Convenience store, Gift shop, Sun umbrellas, Self-serve laundry, Air conditioning, Private beach, Safe, Kitchenette, Refrigerator, Non-smoking rooms, Family rooms, </t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g194838-d676423-Reviews-Conero_Azzurro-Numana_Province_of_Ancona_Marche.html</t>
@@ -806,15 +1090,31 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camping Don Diego</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lungomare Alcide De' Gasperi 128, 63066 Grottammare Italy</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Village and Camping on the sea of the Riviera of the Palms, in the Region Marche, central Italy, adriatic coast. Bungalows in masonry and pitche for camping open air, at 10 mt from the sea by shallow water and fine sand. Clean sea by European Blue Flag.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Business Center with Internet Access, Self-serve laundry, Wifi, Restaurant, Kitchenette, </t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g730082-d1548649-Reviews-Camping_Don_Diego-Grottammare_Province_of_Ascoli_Piceno_Marche.html</t>
@@ -825,15 +1125,31 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Camping Lpre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti 45, 60010 Ostra Italy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Campeggio nella campagna dell'entroterra marchigiano (tra i caselli autostradali di Senigallia e Montemarciano-15/20 min.) situato in borgo tranquillo e caratteristico. Piazzole ampie e ombreggiate da ulivi, servizi igienici pulitissimi. Titolare (e fidanzata) molto gentili e accoglienti. Ottima copertura wifi gratuito in tutta la struttura. Torneremo presto a trovarvi: complimenti e grazie di tutto!!</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free High Speed Internet (WiFi), Wifi, Pets Allowed ( Dog / Pet Friendly ), </t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g2140648-d3519310-Reviews-Camping_Lpre-Ostra_Province_of_Ancona_Marche.html</t>
@@ -844,15 +1160,31 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Camping Paradiso</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Via Rive del Faro 2, 61121, Pesaro Italy</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We stayed here in a Tendi tent for a week. Camping is nice, not too big. Beautiful scenery and shady places. Suitable for smaller children.   Pool has very strict rules, which we found very patronizing.   Small shop available,  bread every morning which was great!   </t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Pool, Bar / lounge, Restaurant, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Self-serve laundry, Seating area, Sofa, Kitchenette, Refrigerator, Kitchenware, </t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g187796-d4116318-Reviews-Camping_Paradiso-Pesaro_Province_of_Pesaro_and_Urbino_Marche.html</t>
@@ -863,15 +1195,31 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Camping Bellamare</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Viale Scarfiotti 13, 62017 Porto Recanati Italy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The Bellamare Camping is immersed in the enchanting Conero Riviera covering an area of 50,000 sq mt. It is the perfect starting point for excursions and visits to places of major touristic interest in the Marche. The Camping Bellamare is directly by the beach of Porto Recanati far away from the railway, which is quite an exceptional location along the Adriatic coast of Marche. The campsite offers various types of accommodations such as pleasant bungalows, beachfront apartments and finely curated lown grass pitches each one surrounded by trees. The entetainment team of the campsite organizes fun activities, games, kids club, evening shows, sports for adults and kids. Porto Recanati is an oasis of peace and tranquility in the beautiful scenery of Mount Conero, the ideal place for your holiday in the Marche.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Fitness classes, Bar / lounge, Beach, Bicycle rental, Children's playground, Wifi, Paid wifi, Adult pool, Outdoor pool, Plunge pool, Shallow end in pool, Coffee shop, Restaurant, Breakfast available, Outdoor dining area, Snack bar, Wine / champagne, Swimup bar, Poolside bar, Game room, Hiking, Aerobics, Entertainment staff, Evening entertainment, Indoor play area for children, Children Activities (Kid / Family Friendly), Kids club, Kids' outdoor play equipment, Highchairs available, Concierge, Convenience store, Sun deck, Sun loungers / beach chairs, Sun terrace, Sun umbrellas, Infirmary, Express check-in / check-out, Clothes dryer, Laundry service, Self-serve laundry, Washing machine, Allergy-free room, Air conditioning, Dining area, Housekeeping, Clothes rack, Microwave, Stovetop, Walk-in shower, Kitchenware, Hair dryer, Family rooms, </t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g194858-d1815916-Reviews-Camping_Bellamare-Porto_Recanati_Province_of_Macerata_Marche.html</t>
@@ -882,15 +1230,31 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Camping Reno</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Via Moricone 7, 60020 Sirolo Italy</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The location of this campsite is excellent, although on a steep hill, it is possible to walk into the centre of the beautiful town in 10 minutes.   The campsite is very basic with fairly poor, unrenovated sanitaire.  Staff are very pleasant and helpful.  Sirolo is worth a visit, and has great views over the sea.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bar / lounge, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g608900-d4817085-Reviews-Camping_Reno-Sirolo_Province_of_Ancona_Marche.html</t>
@@ -901,15 +1265,31 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camping Summerland</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Via Francesco Podesti 236, 60019, Senigallia Italy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The Camping Holiday Center Summerland rises in a quiet and shady area within the residential zone of Senigallia. The so-called "Spiaggia di Velluto" (“Velvet beach”), famous for its wonderful sandy beach, is only 150 m. far from the camping. It’s the ideal place for children because of the knee-deep water; tourists can choose between free beach (free access) or private beach (with beach facilities on charge). The camping extends on a 45.000 square meters area of grassy ground and has: 176 little squares, 89 bungalows, 10 chalets, 3 restrooms located in different areas with free hot water in showers and washbasins (no coins!!!), two inside parking places and an outside one. Our strong points are the green areas, 3 swimming pools with solarium and sports facilities (soccer and volley grounds, tennis court) all free-access. A friendly staff will welcome you at the camping. We work for families from more than 40 years; for that reason we can satisfy both adults and children needs.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Tennis court, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Restaurant, Evening entertainment, Kids' outdoor play equipment, Pets Allowed ( Dog / Pet Friendly ), Concierge, Convenience store, Laundry service, Self-serve laundry, Air conditioning, Kitchenette, Microwave, Refrigerator, Family rooms, </t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g194914-d2316135-Reviews-Camping_Summerland-Senigallia_Province_of_Ancona_Marche.html</t>
@@ -920,15 +1300,31 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Camping Gabicce Monte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Via Panoramica 148, 61011 Gabicce Monte Italy</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Camping Gabicce Monte is a small and intimate camp, surrounded by the San Bartolo natural park. A cool and shaded terrace overlooking the sea from which to enjoy a beautiful landscape. Located halfway between the sea and Gabicce Vallugola, Camping Gabicce Monte is perfect for lovers of hiking or biking. The beaches of Gabicce and Cattolica are easily reachable on foot in 15 minutes through scenic trails. The bay cobbled below the campground is instead reached in about ten minutes through a path in the wild and enchanting forest. From the rooftop terrace of Gabicce Monte, just 500 meters from the campsite, there are buses and shuttles every half hour to the beaches. Finally, for the very young or the nightlife lovers, the campsite is just a few minutes by car or on foot from bar and pubs of Gabicce and Cattolica and one of the most famous discos of the Riviera: the Baia Imperiale.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Wifi, Breakfast available, Pets Allowed ( Dog / Pet Friendly ), BBQ facilities, Concierge, Self-serve laundry, Non-smoking hotel, Air conditioning, Kitchenette, Refrigerator, Ocean view, Non-smoking rooms, Family rooms, </t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g2275905-d2250335-Reviews-Camping_Gabicce_Monte-Gabicce_Monte_Province_of_Pesaro_and_Urbino_Marche.html</t>
@@ -939,15 +1335,31 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Camping Club Internazionale</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Via San Michele 10, 60020 Sirolo Italy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>The site is beautiful, servise is nice, food is good in restaurant, good choice in the shop, clean bathrooms, short walk to the beach and downtown. While the quite hours are respected within the camping itself it is of no use at all, because of the noise from Sirolo till late night. Everynight. Is like your tent is placed in some bar. Was tired everyday we stayed in the camping. This canceled all the good points the camping offers, i did not enjoy my stay at all and do not advice for anyone who cant sleep in noisy places.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>non disponibile</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Bicycle rental, Table tennis, Books, DVDs, music for children, Children Activities (Kid / Family Friendly), Wifi, Paid wifi, Outdoor pool, Shallow end in pool, Fence around pool, Restaurant, Special diet menus, Vending machine, Tennis court offsite, Kids club, Kids' outdoor play equipment, BBQ facilities, Concierge, Convenience store, Newspaper, Outdoor furniture, Picnic area, Sun loungers / beach chairs, Sun terrace, Self-serve laundry, Ocean view, </t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>

--- a/datasets/general_data_dataset_tripadvisor.xlsx
+++ b/datasets/general_data_dataset_tripadvisor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miles\Downloads\progetto_bda-main\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simo\Desktop\progetto_bda-main\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D35372-4ACE-4704-89B2-511B69AB817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6F6CDD-267E-400A-8CC8-CD3F765104DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1305" yWindow="915" windowWidth="31755" windowHeight="13755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="165">
   <si>
     <t>name</t>
   </si>
@@ -434,13 +434,94 @@
   </si>
   <si>
     <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Camping-Club-Internazionale-Sirolo</t>
+  </si>
+  <si>
+    <t>La-Risacca-Camping-Village-Formule-Hotel-Porto-Sant-Elpidio</t>
+  </si>
+  <si>
+    <t>Reviews-Girasole-Eco-Family-Village-Marina-Palmense-Fermo</t>
+  </si>
+  <si>
+    <t>Green-Garden-Camping-Village-Sirolo</t>
+  </si>
+  <si>
+    <t>Centro-Vacanze-Garden-River-Altidona</t>
+  </si>
+  <si>
+    <t>Amapolas-Villaggio-Camping-Mombaroccio</t>
+  </si>
+  <si>
+    <t>Villaggio-Turistico-Residence-Mare-Fermo</t>
+  </si>
+  <si>
+    <t>Camping-Villaggio-Cortina-Senigallia</t>
+  </si>
+  <si>
+    <t>La-Mimosa-Camping-Fano</t>
+  </si>
+  <si>
+    <t>Camping-Vettore-Montegallo</t>
+  </si>
+  <si>
+    <t>Camping-Monte-Prata-Castelsantangelo-sul-Nera</t>
+  </si>
+  <si>
+    <t>Camping-Centro-Turistico-Belvedere-Civitanova-Marche</t>
+  </si>
+  <si>
+    <t>Camping-Stella-Maris-Fano</t>
+  </si>
+  <si>
+    <t>Conero-Azzurro-Numana</t>
+  </si>
+  <si>
+    <t>Camping-Don-Diego-Grottammare</t>
+  </si>
+  <si>
+    <t>Camping-Lpre-Ostra</t>
+  </si>
+  <si>
+    <t>Camping-Bellamare-Porto-Recanati</t>
+  </si>
+  <si>
+    <t>Camping-Reno-Sirolo</t>
+  </si>
+  <si>
+    <t>Camping-Summerland-Senigallia</t>
+  </si>
+  <si>
+    <t>Camping-Gabicce-Monte-Gabicce-Monte</t>
+  </si>
+  <si>
+    <t>villaggio-camping-blu</t>
+  </si>
+  <si>
+    <t>Natural-Village-Resort-Porto-Potenza-Picena</t>
+  </si>
+  <si>
+    <t>camping-village-mar-y-sierra</t>
+  </si>
+  <si>
+    <t>glamping-poggio-imperiale-marche-1</t>
+  </si>
+  <si>
+    <t>civettuola</t>
+  </si>
+  <si>
+    <t>camping-paradiso</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +534,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -462,7 +551,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -485,17 +574,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -796,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -804,10 +910,11 @@
     <col min="4" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="48.85546875" customWidth="1"/>
+    <col min="7" max="7" width="58.28515625" customWidth="1"/>
+    <col min="8" max="8" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -826,8 +933,11 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -846,11 +956,14 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -869,11 +982,14 @@
       <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -892,11 +1008,14 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -915,11 +1034,14 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -938,11 +1060,14 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -961,11 +1086,14 @@
       <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -984,11 +1112,14 @@
       <c r="F8" t="s">
         <v>42</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1007,11 +1138,14 @@
       <c r="F9" t="s">
         <v>47</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1030,11 +1164,14 @@
       <c r="F10" t="s">
         <v>52</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1053,11 +1190,14 @@
       <c r="F11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1073,11 +1213,14 @@
       <c r="E12" t="s">
         <v>9</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1096,11 +1239,14 @@
       <c r="F13" t="s">
         <v>66</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1119,11 +1265,14 @@
       <c r="F14" t="s">
         <v>71</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1142,11 +1291,14 @@
       <c r="F15" t="s">
         <v>76</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1165,11 +1317,14 @@
       <c r="F16" t="s">
         <v>81</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1188,11 +1343,14 @@
       <c r="F17" t="s">
         <v>86</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1211,11 +1369,14 @@
       <c r="F18" t="s">
         <v>91</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1234,11 +1395,14 @@
       <c r="F19" t="s">
         <v>96</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1257,11 +1421,14 @@
       <c r="F20" t="s">
         <v>101</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1280,11 +1447,14 @@
       <c r="F21" t="s">
         <v>106</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1303,11 +1473,14 @@
       <c r="F22" t="s">
         <v>111</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1326,11 +1499,14 @@
       <c r="F23" t="s">
         <v>116</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1349,11 +1525,14 @@
       <c r="F24" t="s">
         <v>121</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1372,11 +1551,14 @@
       <c r="F25" t="s">
         <v>126</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1395,11 +1577,14 @@
       <c r="F26" t="s">
         <v>131</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1418,11 +1603,42 @@
       <c r="F27" t="s">
         <v>136</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="3" t="s">
         <v>137</v>
       </c>
+      <c r="H27" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{960FFFA2-0633-459B-BD9F-4613A7083B9E}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{A550377A-ED7F-4FE3-9A08-E88FB202DD51}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{89F969BC-1B33-49C6-83FF-F6DFB5E88FDF}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{8EFDDA4E-481D-4973-9741-459E5AE67D89}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{3723E773-C5EC-459E-8355-BE11A1A7908D}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{2CB56719-C23B-4A39-B82B-82CA434F36F1}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{E2691E92-57F9-400F-990B-AC0DD1436005}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{76F55FA6-2A1C-4403-87E0-CCC7CEA92161}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{138B2497-3E07-4448-8C2B-204D0C003633}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{728C4F5F-3A49-493A-B5B7-F417E0E17A49}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{D76AF28A-CE57-47D2-80D2-B789E1F1174C}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{EA06E08E-EC50-4C58-AD94-1655DF8D48A0}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{5DE905EF-80BC-446F-A312-9341AB0B50D5}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{45F6B3AD-125F-4155-8206-11F6CD211115}"/>
+    <hyperlink ref="G17" r:id="rId15" xr:uid="{90D28D3D-6AD0-46A1-AB15-FCD8AC4BD65D}"/>
+    <hyperlink ref="G16" r:id="rId16" xr:uid="{FCA5F3AE-F1CE-41F9-9178-F39E1C7B1448}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{4613D0F7-8ED4-4C5C-BA38-AE3D1FE48AF3}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{4F9F2512-E5FE-4029-A500-FCE8AF6DA93A}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{9CED43EB-AF62-4868-8237-33BF89E84C88}"/>
+    <hyperlink ref="G21" r:id="rId20" xr:uid="{F0EAC6EE-0EDC-4629-B250-75F95B540FB4}"/>
+    <hyperlink ref="G22" r:id="rId21" xr:uid="{D93CE2B5-FBF8-4D98-8CE2-B4DE099AA032}"/>
+    <hyperlink ref="G23" r:id="rId22" xr:uid="{020D1DC9-D2E8-4DAB-83FB-E97ABC1D14FE}"/>
+    <hyperlink ref="G24" r:id="rId23" xr:uid="{E9FF066A-24DA-41D9-91F9-466AF64A6831}"/>
+    <hyperlink ref="G25" r:id="rId24" xr:uid="{473D5A4F-10ED-46B2-BABD-8CD49549B516}"/>
+    <hyperlink ref="G26" r:id="rId25" xr:uid="{FC5A67C9-AB48-4C55-979D-3E7FCCF693A1}"/>
+    <hyperlink ref="G27" r:id="rId26" xr:uid="{1255A9CC-CC9D-47E1-9B9F-A9ABFB8CB22C}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/datasets/general_data_dataset_tripadvisor.xlsx
+++ b/datasets/general_data_dataset_tripadvisor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simo\Desktop\progetto_bda-main\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miles\Downloads\progetto_bda-main\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6F6CDD-267E-400A-8CC8-CD3F765104DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C5F11-731E-4610-99FD-77086112D99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="915" windowWidth="31755" windowHeight="13755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -436,92 +436,92 @@
     <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>Camping-Club-Internazionale-Sirolo</t>
-  </si>
-  <si>
-    <t>La-Risacca-Camping-Village-Formule-Hotel-Porto-Sant-Elpidio</t>
-  </si>
-  <si>
-    <t>Reviews-Girasole-Eco-Family-Village-Marina-Palmense-Fermo</t>
-  </si>
-  <si>
-    <t>Green-Garden-Camping-Village-Sirolo</t>
-  </si>
-  <si>
-    <t>Centro-Vacanze-Garden-River-Altidona</t>
-  </si>
-  <si>
-    <t>Amapolas-Villaggio-Camping-Mombaroccio</t>
-  </si>
-  <si>
-    <t>Villaggio-Turistico-Residence-Mare-Fermo</t>
-  </si>
-  <si>
-    <t>Camping-Villaggio-Cortina-Senigallia</t>
-  </si>
-  <si>
-    <t>La-Mimosa-Camping-Fano</t>
-  </si>
-  <si>
-    <t>Camping-Vettore-Montegallo</t>
-  </si>
-  <si>
-    <t>Camping-Monte-Prata-Castelsantangelo-sul-Nera</t>
-  </si>
-  <si>
-    <t>Camping-Centro-Turistico-Belvedere-Civitanova-Marche</t>
-  </si>
-  <si>
-    <t>Camping-Stella-Maris-Fano</t>
-  </si>
-  <si>
-    <t>Conero-Azzurro-Numana</t>
-  </si>
-  <si>
-    <t>Camping-Don-Diego-Grottammare</t>
-  </si>
-  <si>
-    <t>Camping-Lpre-Ostra</t>
-  </si>
-  <si>
-    <t>Camping-Bellamare-Porto-Recanati</t>
-  </si>
-  <si>
-    <t>Camping-Reno-Sirolo</t>
-  </si>
-  <si>
-    <t>Camping-Summerland-Senigallia</t>
-  </si>
-  <si>
-    <t>Camping-Gabicce-Monte-Gabicce-Monte</t>
-  </si>
-  <si>
-    <t>villaggio-camping-blu</t>
-  </si>
-  <si>
-    <t>Natural-Village-Resort-Porto-Potenza-Picena</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>natural-village-resort</t>
+  </si>
+  <si>
+    <t>casale-civetta</t>
+  </si>
+  <si>
+    <t>conero-azzurro</t>
+  </si>
+  <si>
+    <t>green-garden-camping-village</t>
+  </si>
+  <si>
+    <t>amapolas-villaggio-&amp;-camping</t>
+  </si>
+  <si>
+    <t>camping-villaggio-cortina</t>
+  </si>
+  <si>
+    <t>camping-vettore</t>
+  </si>
+  <si>
+    <t>camping-gabicce-monte</t>
+  </si>
+  <si>
+    <t>la-mimosa-camping</t>
+  </si>
+  <si>
+    <t>camping-lpre</t>
+  </si>
+  <si>
+    <t>camping-don-diego</t>
+  </si>
+  <si>
+    <t>camping-monte-prata</t>
+  </si>
+  <si>
+    <t>camping-paradiso</t>
+  </si>
+  <si>
+    <t>camping-centro-turistico-belvedere</t>
+  </si>
+  <si>
+    <t>camping-bellamare</t>
+  </si>
+  <si>
+    <t>la-risacca-camping-village</t>
+  </si>
+  <si>
+    <t>centro-vacanze-garden-river</t>
+  </si>
+  <si>
+    <t>residence-mare</t>
+  </si>
+  <si>
+    <t>camping-reno</t>
+  </si>
+  <si>
+    <t>girasole-eco-family-village</t>
+  </si>
+  <si>
+    <t>camping-blu-fantasy</t>
   </si>
   <si>
     <t>camping-village-mar-y-sierra</t>
   </si>
   <si>
-    <t>glamping-poggio-imperiale-marche-1</t>
-  </si>
-  <si>
-    <t>civettuola</t>
-  </si>
-  <si>
-    <t>camping-paradiso</t>
+    <t>camping-stella-maris</t>
+  </si>
+  <si>
+    <t>camping-summerland</t>
+  </si>
+  <si>
+    <t>poggio-imperiale-marche</t>
+  </si>
+  <si>
+    <t>camping-club-internazionale</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,14 +533,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -586,11 +578,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -598,10 +589,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -905,13 +894,13 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="20.5703125" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="58.28515625" customWidth="1"/>
-    <col min="8" max="8" width="73" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -956,11 +945,11 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -982,11 +971,11 @@
       <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1008,11 +997,11 @@
       <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1034,7 +1023,7 @@
       <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>27</v>
       </c>
       <c r="H5" t="s">
@@ -1060,7 +1049,7 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>32</v>
       </c>
       <c r="H6" t="s">
@@ -1086,11 +1075,11 @@
       <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1112,11 +1101,11 @@
       <c r="F8" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1138,11 +1127,11 @@
       <c r="F9" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1164,11 +1153,11 @@
       <c r="F10" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" t="s">
         <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1190,11 +1179,11 @@
       <c r="F11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1213,11 +1202,11 @@
       <c r="E12" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" t="s">
         <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1239,11 +1228,11 @@
       <c r="F13" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" t="s">
         <v>67</v>
       </c>
       <c r="H13" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1265,7 +1254,7 @@
       <c r="F14" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" t="s">
         <v>72</v>
       </c>
       <c r="H14" t="s">
@@ -1291,11 +1280,11 @@
       <c r="F15" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" t="s">
         <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1317,11 +1306,11 @@
       <c r="F16" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" t="s">
         <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1343,11 +1332,11 @@
       <c r="F17" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" t="s">
         <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1369,11 +1358,11 @@
       <c r="F18" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" t="s">
         <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1395,11 +1384,11 @@
       <c r="F19" t="s">
         <v>96</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" t="s">
         <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1421,11 +1410,11 @@
       <c r="F20" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" t="s">
         <v>102</v>
       </c>
       <c r="H20" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1447,11 +1436,11 @@
       <c r="F21" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" t="s">
         <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1473,11 +1462,11 @@
       <c r="F22" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" t="s">
         <v>112</v>
       </c>
       <c r="H22" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1499,11 +1488,11 @@
       <c r="F23" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" t="s">
         <v>117</v>
       </c>
       <c r="H23" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1525,11 +1514,11 @@
       <c r="F24" t="s">
         <v>121</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" t="s">
         <v>122</v>
       </c>
       <c r="H24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1551,11 +1540,11 @@
       <c r="F25" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" t="s">
         <v>127</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1577,11 +1566,11 @@
       <c r="F26" t="s">
         <v>131</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" t="s">
         <v>132</v>
       </c>
       <c r="H26" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1603,42 +1592,15 @@
       <c r="F27" t="s">
         <v>136</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" t="s">
         <v>137</v>
       </c>
       <c r="H27" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{960FFFA2-0633-459B-BD9F-4613A7083B9E}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{A550377A-ED7F-4FE3-9A08-E88FB202DD51}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{89F969BC-1B33-49C6-83FF-F6DFB5E88FDF}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{8EFDDA4E-481D-4973-9741-459E5AE67D89}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{3723E773-C5EC-459E-8355-BE11A1A7908D}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{2CB56719-C23B-4A39-B82B-82CA434F36F1}"/>
-    <hyperlink ref="G8" r:id="rId7" xr:uid="{E2691E92-57F9-400F-990B-AC0DD1436005}"/>
-    <hyperlink ref="G9" r:id="rId8" xr:uid="{76F55FA6-2A1C-4403-87E0-CCC7CEA92161}"/>
-    <hyperlink ref="G10" r:id="rId9" xr:uid="{138B2497-3E07-4448-8C2B-204D0C003633}"/>
-    <hyperlink ref="G11" r:id="rId10" xr:uid="{728C4F5F-3A49-493A-B5B7-F417E0E17A49}"/>
-    <hyperlink ref="G12" r:id="rId11" xr:uid="{D76AF28A-CE57-47D2-80D2-B789E1F1174C}"/>
-    <hyperlink ref="G13" r:id="rId12" xr:uid="{EA06E08E-EC50-4C58-AD94-1655DF8D48A0}"/>
-    <hyperlink ref="G14" r:id="rId13" xr:uid="{5DE905EF-80BC-446F-A312-9341AB0B50D5}"/>
-    <hyperlink ref="G15" r:id="rId14" xr:uid="{45F6B3AD-125F-4155-8206-11F6CD211115}"/>
-    <hyperlink ref="G17" r:id="rId15" xr:uid="{90D28D3D-6AD0-46A1-AB15-FCD8AC4BD65D}"/>
-    <hyperlink ref="G16" r:id="rId16" xr:uid="{FCA5F3AE-F1CE-41F9-9178-F39E1C7B1448}"/>
-    <hyperlink ref="G18" r:id="rId17" xr:uid="{4613D0F7-8ED4-4C5C-BA38-AE3D1FE48AF3}"/>
-    <hyperlink ref="G19" r:id="rId18" xr:uid="{4F9F2512-E5FE-4029-A500-FCE8AF6DA93A}"/>
-    <hyperlink ref="G20" r:id="rId19" xr:uid="{9CED43EB-AF62-4868-8237-33BF89E84C88}"/>
-    <hyperlink ref="G21" r:id="rId20" xr:uid="{F0EAC6EE-0EDC-4629-B250-75F95B540FB4}"/>
-    <hyperlink ref="G22" r:id="rId21" xr:uid="{D93CE2B5-FBF8-4D98-8CE2-B4DE099AA032}"/>
-    <hyperlink ref="G23" r:id="rId22" xr:uid="{020D1DC9-D2E8-4DAB-83FB-E97ABC1D14FE}"/>
-    <hyperlink ref="G24" r:id="rId23" xr:uid="{E9FF066A-24DA-41D9-91F9-466AF64A6831}"/>
-    <hyperlink ref="G25" r:id="rId24" xr:uid="{473D5A4F-10ED-46B2-BABD-8CD49549B516}"/>
-    <hyperlink ref="G26" r:id="rId25" xr:uid="{FC5A67C9-AB48-4C55-979D-3E7FCCF693A1}"/>
-    <hyperlink ref="G27" r:id="rId26" xr:uid="{1255A9CC-CC9D-47E1-9B9F-A9ABFB8CB22C}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/datasets/general_data_dataset_tripadvisor.xlsx
+++ b/datasets/general_data_dataset_tripadvisor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miles\Downloads\progetto_bda-main\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C5F11-731E-4610-99FD-77086112D99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30838C48-6363-4B52-82F2-6C643C002421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -436,9 +436,6 @@
     <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>natural-village-resort</t>
   </si>
   <si>
@@ -515,6 +512,9 @@
   </si>
   <si>
     <t>camping-club-internazionale</t>
+  </si>
+  <si>
+    <t>id</t>
   </si>
 </sst>
 </file>
@@ -923,7 +923,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -949,7 +949,7 @@
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -975,7 +975,7 @@
         <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1001,7 +1001,7 @@
         <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1027,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1053,7 +1053,7 @@
         <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1079,7 +1079,7 @@
         <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1131,7 +1131,7 @@
         <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
         <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1183,7 +1183,7 @@
         <v>58</v>
       </c>
       <c r="H11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1206,7 +1206,7 @@
         <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1232,7 +1232,7 @@
         <v>67</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1258,7 +1258,7 @@
         <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
         <v>77</v>
       </c>
       <c r="H15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1310,7 +1310,7 @@
         <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1362,7 +1362,7 @@
         <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1388,7 +1388,7 @@
         <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1414,7 +1414,7 @@
         <v>102</v>
       </c>
       <c r="H20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1440,7 +1440,7 @@
         <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1466,7 +1466,7 @@
         <v>112</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>117</v>
       </c>
       <c r="H23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1518,7 +1518,7 @@
         <v>122</v>
       </c>
       <c r="H24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1544,7 +1544,7 @@
         <v>127</v>
       </c>
       <c r="H25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1570,7 +1570,7 @@
         <v>132</v>
       </c>
       <c r="H26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1596,7 +1596,7 @@
         <v>137</v>
       </c>
       <c r="H27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
